--- a/feedback_forms/013_diversity_and_inclusion_survey--feedback_forms.xlsx
+++ b/feedback_forms/013_diversity_and_inclusion_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Non-Binary'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Prefer Not To Say'}</t>
+          <t>Prefer Not To Say</t>
         </is>
       </c>
     </row>
